--- a/artfynd/S 2887-2025 artfynd.xlsx
+++ b/artfynd/S 2887-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AZ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79390030</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96631938</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -969,6 +984,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96632335</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1067,6 +1087,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96632396</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1168,6 +1193,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126711181</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1266,6 +1296,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96632124</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1367,6 +1402,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96636901</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1465,6 +1505,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86381803</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1563,6 +1608,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96632591</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>ÅGP: Vildbin på ängsmark</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87438692</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1798,6 +1853,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/12997143</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1910,6 +1970,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13768408</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2025,6 +2090,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79427632</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2137,6 +2207,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95290822</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2268,6 +2343,11 @@
           <t>Personlig inventering NES</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131239489</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2401,6 +2481,11 @@
           <t>ÅGP: Vildbin på ängsmark</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79456680</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2520,6 +2605,11 @@
           <t>ÅGP: Vildbin på ängsmark</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87436534</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2647,6 +2737,11 @@
           <t>ÅGP: Vildbin på ängsmark</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87509414</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2759,6 +2854,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95437168</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2871,6 +2971,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95437195</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2983,6 +3088,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95437334</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3098,6 +3208,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102734958</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3213,6 +3328,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111158096</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3328,6 +3448,11 @@
           <t>FRN0001 inventering guldsandbi och silvergökbi Finspång</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119355283</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3459,6 +3584,11 @@
           <t>Personlig inventering NES</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131239448</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3605,6 +3735,11 @@
           <t>Personlig inventering NES</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131239476</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3728,6 +3863,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79389774</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3851,6 +3991,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79389825</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3974,6 +4119,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79389831</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4090,6 +4240,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95290850</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4206,6 +4361,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95291147</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4322,6 +4482,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95291733</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4433,6 +4598,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111158107</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4552,6 +4722,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111643611</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4671,6 +4846,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111643612</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4790,6 +4970,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111643613</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4909,6 +5094,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111643614</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5028,6 +5218,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111643615</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5143,6 +5338,11 @@
           <t>FRN0001a Inventering högsommaraktiva vildbin Finspång</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127396151</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5259,6 +5459,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/12997131</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5371,6 +5576,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13768411</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5472,6 +5682,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126654954</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5588,6 +5803,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/12997127</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5700,6 +5920,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13768409</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5825,6 +6050,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111158106</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5973,6 +6203,11 @@
       <c r="AY47" t="inlineStr">
         <is>
           <t>Personlig inventering NES</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131239506</t>
         </is>
       </c>
     </row>
@@ -6083,6 +6318,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79428551</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6194,6 +6434,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/12997140</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6310,6 +6555,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/12997124</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6426,6 +6676,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/12997125</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6542,6 +6797,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/12997132</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6654,6 +6914,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13768410</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6765,6 +7030,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128341186</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6867,6 +7137,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87273576</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6978,6 +7253,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128341128</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7088,6 +7368,11 @@
           <t>FRN0001a Inventering högsommaraktiva vildbin Finspång</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127396155</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7194,8 +7479,72 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102734348</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>